--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/102.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/102.xlsx
@@ -426,13 +426,13 @@
         <v>-17.02671823296951</v>
       </c>
       <c r="E2">
-        <v>-6.427980734687353</v>
+        <v>-7.870775195901166</v>
       </c>
       <c r="F2">
-        <v>-0.696995953237892</v>
+        <v>-1.551388665705362</v>
       </c>
       <c r="G2">
-        <v>-8.552904799378242</v>
+        <v>-10.79481948075485</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.73790868071003</v>
       </c>
       <c r="E3">
-        <v>-6.920551909449673</v>
+        <v>-8.106264901248041</v>
       </c>
       <c r="F3">
-        <v>-0.7467868753663505</v>
+        <v>-1.242884337083673</v>
       </c>
       <c r="G3">
-        <v>-8.706338653486844</v>
+        <v>-10.12828086296906</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.25703088427156</v>
       </c>
       <c r="E4">
-        <v>-7.415156369041436</v>
+        <v>-9.210483474804372</v>
       </c>
       <c r="F4">
-        <v>-0.661626257175425</v>
+        <v>-1.456569816989129</v>
       </c>
       <c r="G4">
-        <v>-7.953715920043392</v>
+        <v>-9.084081831154304</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.79439624480713</v>
       </c>
       <c r="E5">
-        <v>-8.823525370848941</v>
+        <v>-10.5090550958219</v>
       </c>
       <c r="F5">
-        <v>-0.7246997208166742</v>
+        <v>-1.094681137516849</v>
       </c>
       <c r="G5">
-        <v>-7.566388713039742</v>
+        <v>-8.432394320657691</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.35481946780288</v>
       </c>
       <c r="E6">
-        <v>-9.81669670478918</v>
+        <v>-10.25523865616599</v>
       </c>
       <c r="F6">
-        <v>-0.5943187557692485</v>
+        <v>-1.479065567664988</v>
       </c>
       <c r="G6">
-        <v>-6.779525007083609</v>
+        <v>-7.918746627512071</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.998474051774519</v>
       </c>
       <c r="E7">
-        <v>-10.01522953375946</v>
+        <v>-10.87741928550184</v>
       </c>
       <c r="F7">
-        <v>-0.5169792692417209</v>
+        <v>-1.220632477118791</v>
       </c>
       <c r="G7">
-        <v>-6.336448213198632</v>
+        <v>-8.522997330976466</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.72867279168042</v>
       </c>
       <c r="E8">
-        <v>-11.55614696977147</v>
+        <v>-11.20565666699981</v>
       </c>
       <c r="F8">
-        <v>-0.606008089131107</v>
+        <v>-1.501275459423111</v>
       </c>
       <c r="G8">
-        <v>-6.656144285380512</v>
+        <v>-7.161360019037609</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.547230398587327</v>
       </c>
       <c r="E9">
-        <v>-12.3704254665127</v>
+        <v>-12.77464158491137</v>
       </c>
       <c r="F9">
-        <v>-0.6187292068968745</v>
+        <v>-1.21892761770082</v>
       </c>
       <c r="G9">
-        <v>-4.853783977435099</v>
+        <v>-6.812782747571127</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.425448917221221</v>
       </c>
       <c r="E10">
-        <v>-12.50345844743603</v>
+        <v>-13.08705194975253</v>
       </c>
       <c r="F10">
-        <v>-0.5532675147351426</v>
+        <v>-1.181390620093074</v>
       </c>
       <c r="G10">
-        <v>-4.15179934856034</v>
+        <v>-5.837082213509427</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.34758279088364</v>
       </c>
       <c r="E11">
-        <v>-13.81499508953752</v>
+        <v>-15.13936995545076</v>
       </c>
       <c r="F11">
-        <v>-0.5793432326328531</v>
+        <v>-1.189134942019573</v>
       </c>
       <c r="G11">
-        <v>-3.299943012577236</v>
+        <v>-5.198967939723827</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.292391726306145</v>
       </c>
       <c r="E12">
-        <v>-14.41927918959506</v>
+        <v>-15.52506914363206</v>
       </c>
       <c r="F12">
-        <v>-0.2104949575151749</v>
+        <v>-0.990409940044316</v>
       </c>
       <c r="G12">
-        <v>-3.034126069046994</v>
+        <v>-4.260848718623933</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.241006398213041</v>
       </c>
       <c r="E13">
-        <v>-14.09002742991937</v>
+        <v>-15.93983207799459</v>
       </c>
       <c r="F13">
-        <v>-0.3163538201679362</v>
+        <v>-1.21017685066506</v>
       </c>
       <c r="G13">
-        <v>-2.48629037211732</v>
+        <v>-4.184987567591533</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.190337761015233</v>
       </c>
       <c r="E14">
-        <v>-16.11667351646812</v>
+        <v>-17.42470964816168</v>
       </c>
       <c r="F14">
-        <v>-0.4999971907104636</v>
+        <v>-0.9095823412380331</v>
       </c>
       <c r="G14">
-        <v>-1.588698849509184</v>
+        <v>-3.175254625386125</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.142483137195651</v>
       </c>
       <c r="E15">
-        <v>-17.10302949702682</v>
+        <v>-17.80429086795862</v>
       </c>
       <c r="F15">
-        <v>-0.1866783961058388</v>
+        <v>-0.9400449245215108</v>
       </c>
       <c r="G15">
-        <v>-0.9662798721252687</v>
+        <v>-1.989254996487762</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.1064896327672894</v>
       </c>
       <c r="E16">
-        <v>-16.45503203737323</v>
+        <v>-18.68054153149481</v>
       </c>
       <c r="F16">
-        <v>0.04930249567717378</v>
+        <v>-0.8865204156974038</v>
       </c>
       <c r="G16">
-        <v>-0.681907320847413</v>
+        <v>-2.224661268694257</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.8965010719740055</v>
       </c>
       <c r="E17">
-        <v>-19.6015923883889</v>
+        <v>-19.85437180749706</v>
       </c>
       <c r="F17">
-        <v>-0.00439226153284296</v>
+        <v>-0.8596504692831004</v>
       </c>
       <c r="G17">
-        <v>-0.5823625270270677</v>
+        <v>-0.809684447026663</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.830986082103203</v>
       </c>
       <c r="E18">
-        <v>-19.0212412734619</v>
+        <v>-20.86073911469565</v>
       </c>
       <c r="F18">
-        <v>-0.09634460254213044</v>
+        <v>-0.6976801141933617</v>
       </c>
       <c r="G18">
-        <v>0.719698207387065</v>
+        <v>-1.707716272191522</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.657435549377626</v>
       </c>
       <c r="E19">
-        <v>-20.7142339235995</v>
+        <v>-20.54894009384552</v>
       </c>
       <c r="F19">
-        <v>-0.08204373812571222</v>
+        <v>-0.5753903026679162</v>
       </c>
       <c r="G19">
-        <v>0.7778446292388242</v>
+        <v>-0.5596257002633532</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.336504698411316</v>
       </c>
       <c r="E20">
-        <v>-20.19990343123032</v>
+        <v>-21.66274091840208</v>
       </c>
       <c r="F20">
-        <v>0.1636888228316188</v>
+        <v>-0.1645904497032048</v>
       </c>
       <c r="G20">
-        <v>1.027479626173107</v>
+        <v>0.6825538864364423</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.830076352359103</v>
       </c>
       <c r="E21">
-        <v>-21.02186221988856</v>
+        <v>-21.73860644345259</v>
       </c>
       <c r="F21">
-        <v>0.5104657804587751</v>
+        <v>-0.07349806100600097</v>
       </c>
       <c r="G21">
-        <v>1.000627791304079</v>
+        <v>0.783982380668633</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.113755730371684</v>
       </c>
       <c r="E22">
-        <v>-22.84627571420276</v>
+        <v>-22.92008078357977</v>
       </c>
       <c r="F22">
-        <v>0.5815686330913022</v>
+        <v>-0.07483312509271642</v>
       </c>
       <c r="G22">
-        <v>1.272407027350547</v>
+        <v>0.4154425196003466</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.181609407299081</v>
       </c>
       <c r="E23">
-        <v>-22.7452816868837</v>
+        <v>-23.62454831410901</v>
       </c>
       <c r="F23">
-        <v>0.2784362349347839</v>
+        <v>-0.182293114425987</v>
       </c>
       <c r="G23">
-        <v>1.352313665031935</v>
+        <v>0.3463977818333067</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.042828293395167</v>
       </c>
       <c r="E24">
-        <v>-22.30825224582545</v>
+        <v>-24.31117818552202</v>
       </c>
       <c r="F24">
-        <v>0.08791720516037611</v>
+        <v>-0.3852767016078609</v>
       </c>
       <c r="G24">
-        <v>1.457532733906592</v>
+        <v>-0.01232631171104054</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.723761707679171</v>
       </c>
       <c r="E25">
-        <v>-21.60255749884015</v>
+        <v>-24.27365524989447</v>
       </c>
       <c r="F25">
-        <v>-0.0622220748880721</v>
+        <v>-0.07645008883238009</v>
       </c>
       <c r="G25">
-        <v>1.186534786607391</v>
+        <v>-0.2554428444784987</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.263237765360423</v>
       </c>
       <c r="E26">
-        <v>-22.30753674693224</v>
+        <v>-24.23632703864924</v>
       </c>
       <c r="F26">
-        <v>0.3889274373902056</v>
+        <v>-1.063499551747762</v>
       </c>
       <c r="G26">
-        <v>0.9408724443202338</v>
+        <v>0.3258823311264432</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.705295004685913</v>
       </c>
       <c r="E27">
-        <v>-22.9028589969286</v>
+        <v>-23.51200214959637</v>
       </c>
       <c r="F27">
-        <v>0.1888879595051335</v>
+        <v>-0.4438009700070103</v>
       </c>
       <c r="G27">
-        <v>1.074896569932088</v>
+        <v>-0.2301933136504773</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.095678315611461</v>
       </c>
       <c r="E28">
-        <v>-22.42925759978441</v>
+        <v>-24.2722604799001</v>
       </c>
       <c r="F28">
-        <v>0.3060544823941325</v>
+        <v>-0.5060160650420913</v>
       </c>
       <c r="G28">
-        <v>1.107012172208558</v>
+        <v>-0.7161218089957807</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.478515964448326</v>
       </c>
       <c r="E29">
-        <v>-22.38566198051257</v>
+        <v>-23.7014735020773</v>
       </c>
       <c r="F29">
-        <v>-0.008331729997498585</v>
+        <v>-0.2496117017735716</v>
       </c>
       <c r="G29">
-        <v>0.7872134731149617</v>
+        <v>0.3909842091562111</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.8898380112209974</v>
       </c>
       <c r="E30">
-        <v>-22.0146214626941</v>
+        <v>-23.38214362895242</v>
       </c>
       <c r="F30">
-        <v>0.03421769683261305</v>
+        <v>-0.2333090330800379</v>
       </c>
       <c r="G30">
-        <v>1.007973891855722</v>
+        <v>-0.9341940647586524</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.3546468935993445</v>
       </c>
       <c r="E31">
-        <v>-21.57247031753318</v>
+        <v>-23.55562041123826</v>
       </c>
       <c r="F31">
-        <v>0.1250741133484164</v>
+        <v>-0.6178589604963405</v>
       </c>
       <c r="G31">
-        <v>1.562020172217069</v>
+        <v>-0.3693090583017312</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.1130817046123271</v>
       </c>
       <c r="E32">
-        <v>-22.16167007067117</v>
+        <v>-23.14274585053693</v>
       </c>
       <c r="F32">
-        <v>-0.08413422993409229</v>
+        <v>-0.276970221462788</v>
       </c>
       <c r="G32">
-        <v>0.293041719376873</v>
+        <v>-0.3502072105401364</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.5106517667483366</v>
       </c>
       <c r="E33">
-        <v>-20.74017755118944</v>
+        <v>-22.80683270559595</v>
       </c>
       <c r="F33">
-        <v>-0.04951758603441685</v>
+        <v>-0.411305700181066</v>
       </c>
       <c r="G33">
-        <v>0.8106256511686875</v>
+        <v>0.2848911562591874</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.8434861957439902</v>
       </c>
       <c r="E34">
-        <v>-20.71896617893751</v>
+        <v>-21.41647344491695</v>
       </c>
       <c r="F34">
-        <v>-0.02813913988189976</v>
+        <v>-0.3093372111095817</v>
       </c>
       <c r="G34">
-        <v>0.6284794355979868</v>
+        <v>-0.6435149242284851</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.124138013544109</v>
       </c>
       <c r="E35">
-        <v>-19.93739232147968</v>
+        <v>-22.25996512748167</v>
       </c>
       <c r="F35">
-        <v>-0.006445536252210203</v>
+        <v>-0.5591557333287465</v>
       </c>
       <c r="G35">
-        <v>0.3569716642857389</v>
+        <v>-0.5642472218361758</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.370117280921677</v>
       </c>
       <c r="E36">
-        <v>-19.57450758534902</v>
+        <v>-21.40914184549854</v>
       </c>
       <c r="F36">
-        <v>0.1066469031693207</v>
+        <v>-0.2050359232246552</v>
       </c>
       <c r="G36">
-        <v>0.5666483765610189</v>
+        <v>-0.6826124670472777</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.598527033690692</v>
       </c>
       <c r="E37">
-        <v>-18.47689152689587</v>
+        <v>-21.20754776809908</v>
       </c>
       <c r="F37">
-        <v>0.2751627148075706</v>
+        <v>-0.2913605652634286</v>
       </c>
       <c r="G37">
-        <v>1.228691273504471</v>
+        <v>-0.1804159509219958</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.825520387755563</v>
       </c>
       <c r="E38">
-        <v>-17.93680307437107</v>
+        <v>-20.11053399668895</v>
       </c>
       <c r="F38">
-        <v>0.3127250517099634</v>
+        <v>-0.387118551587517</v>
       </c>
       <c r="G38">
-        <v>0.5718360014210567</v>
+        <v>-1.526248718456372</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.064656223923753</v>
       </c>
       <c r="E39">
-        <v>-17.64565842346992</v>
+        <v>-20.67229119734045</v>
       </c>
       <c r="F39">
-        <v>0.4233872944042525</v>
+        <v>0.2202397936601306</v>
       </c>
       <c r="G39">
-        <v>0.4666003798187043</v>
+        <v>-0.3412753586751828</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.325607016138535</v>
       </c>
       <c r="E40">
-        <v>-16.47349462590251</v>
+        <v>-18.58387672532708</v>
       </c>
       <c r="F40">
-        <v>0.6539503282505468</v>
+        <v>0.1138218828192192</v>
       </c>
       <c r="G40">
-        <v>0.1057972636756947</v>
+        <v>-1.216570357076328</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.616583665647761</v>
       </c>
       <c r="E41">
-        <v>-16.49517695945123</v>
+        <v>-17.83076432700746</v>
       </c>
       <c r="F41">
-        <v>0.5196378132680426</v>
+        <v>0.1273601928373533</v>
       </c>
       <c r="G41">
-        <v>0.7177780909742878</v>
+        <v>-1.382849127877301</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.93968475612361</v>
       </c>
       <c r="E42">
-        <v>-16.29538068623281</v>
+        <v>-18.52031959262943</v>
       </c>
       <c r="F42">
-        <v>0.7349838088258369</v>
+        <v>0.2290341126085658</v>
       </c>
       <c r="G42">
-        <v>-0.05034461668403085</v>
+        <v>-0.9962469303467515</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.289340239643182</v>
       </c>
       <c r="E43">
-        <v>-15.40737863264671</v>
+        <v>-16.71112629945501</v>
       </c>
       <c r="F43">
-        <v>1.07276769241217</v>
+        <v>0.004920721102898712</v>
       </c>
       <c r="G43">
-        <v>-0.4324014351891615</v>
+        <v>-2.490812577323965</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.65795460654928</v>
       </c>
       <c r="E44">
-        <v>-13.84731480853027</v>
+        <v>-17.33547606784053</v>
       </c>
       <c r="F44">
-        <v>0.7738542868143827</v>
+        <v>0.1923404384007915</v>
       </c>
       <c r="G44">
-        <v>-0.2056058919303103</v>
+        <v>-1.979598135149708</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.038699865271223</v>
       </c>
       <c r="E45">
-        <v>-14.16780849947512</v>
+        <v>-15.41535780384823</v>
       </c>
       <c r="F45">
-        <v>0.7512405500478229</v>
+        <v>0.07709257522834749</v>
       </c>
       <c r="G45">
-        <v>-1.550226999797313</v>
+        <v>-1.869793960703161</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.422131870772216</v>
       </c>
       <c r="E46">
-        <v>-13.36318018084424</v>
+        <v>-15.1551562158415</v>
       </c>
       <c r="F46">
-        <v>0.7819913678079107</v>
+        <v>0.6891513596330193</v>
       </c>
       <c r="G46">
-        <v>-1.841836403624016</v>
+        <v>-3.147664538861839</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.799682137686627</v>
       </c>
       <c r="E47">
-        <v>-12.80199356791769</v>
+        <v>-14.58187404884047</v>
       </c>
       <c r="F47">
-        <v>0.9025747362094702</v>
+        <v>-0.1062649363964431</v>
       </c>
       <c r="G47">
-        <v>-1.642187333787188</v>
+        <v>-3.143777958398735</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.172879084005646</v>
       </c>
       <c r="E48">
-        <v>-11.92359640770186</v>
+        <v>-14.61770786366316</v>
       </c>
       <c r="F48">
-        <v>1.165235529696933</v>
+        <v>0.4635714564496553</v>
       </c>
       <c r="G48">
-        <v>-2.128569373871372</v>
+        <v>-3.334011836721875</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.542914792301449</v>
       </c>
       <c r="E49">
-        <v>-11.37167958106902</v>
+        <v>-13.87635591234146</v>
       </c>
       <c r="F49">
-        <v>1.368656219711469</v>
+        <v>0.5097816195033052</v>
       </c>
       <c r="G49">
-        <v>-1.917594927744698</v>
+        <v>-3.431874873408271</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.908533540512142</v>
       </c>
       <c r="E50">
-        <v>-10.79788116803112</v>
+        <v>-13.36847849543321</v>
       </c>
       <c r="F50">
-        <v>1.092171257288135</v>
+        <v>0.423589216908471</v>
       </c>
       <c r="G50">
-        <v>-2.488856044910255</v>
+        <v>-3.659776138877239</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.275576202075325</v>
       </c>
       <c r="E51">
-        <v>-10.65451420942228</v>
+        <v>-13.06622096931724</v>
       </c>
       <c r="F51">
-        <v>0.9955667801522436</v>
+        <v>0.8039795407378719</v>
       </c>
       <c r="G51">
-        <v>-2.782673582611652</v>
+        <v>-3.238519150641598</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.64704863782837</v>
       </c>
       <c r="E52">
-        <v>-9.799832667584615</v>
+        <v>-12.14687734712406</v>
       </c>
       <c r="F52">
-        <v>1.004308836805469</v>
+        <v>0.6893778295789271</v>
       </c>
       <c r="G52">
-        <v>-3.295218864092695</v>
+        <v>-3.354537219065357</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.021396420410587</v>
       </c>
       <c r="E53">
-        <v>-9.819404732245767</v>
+        <v>-12.47429507482664</v>
       </c>
       <c r="F53">
-        <v>0.8465416372153071</v>
+        <v>0.6633987177420585</v>
       </c>
       <c r="G53">
-        <v>-3.617603099252463</v>
+        <v>-4.304001679728333</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.399261697580886</v>
       </c>
       <c r="E54">
-        <v>-8.708067397549376</v>
+        <v>-11.2071872912144</v>
       </c>
       <c r="F54">
-        <v>0.9725412798476695</v>
+        <v>0.7287012474592887</v>
       </c>
       <c r="G54">
-        <v>-3.385646415497888</v>
+        <v>-4.358595886216454</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.784111309120268</v>
       </c>
       <c r="E55">
-        <v>-8.565954826240667</v>
+        <v>-9.84443813656017</v>
       </c>
       <c r="F55">
-        <v>1.021031187566595</v>
+        <v>0.4537469368032267</v>
       </c>
       <c r="G55">
-        <v>-4.103856028060615</v>
+        <v>-4.676414879077567</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.174539037357842</v>
       </c>
       <c r="E56">
-        <v>-8.722128309343194</v>
+        <v>-9.637269507657265</v>
       </c>
       <c r="F56">
-        <v>0.9773272391241276</v>
+        <v>0.5451212251533788</v>
       </c>
       <c r="G56">
-        <v>-4.109116484922517</v>
+        <v>-4.119028258267095</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.564202211893647</v>
       </c>
       <c r="E57">
-        <v>-7.763590744613617</v>
+        <v>-10.47465680725964</v>
       </c>
       <c r="F57">
-        <v>1.362631802409137</v>
+        <v>0.176667292808645</v>
       </c>
       <c r="G57">
-        <v>-3.871028670829212</v>
+        <v>-4.527238386532468</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.956560911123292</v>
       </c>
       <c r="E58">
-        <v>-7.424154446894677</v>
+        <v>-9.245669717843972</v>
       </c>
       <c r="F58">
-        <v>0.9774634378328553</v>
+        <v>0.3679235376866899</v>
       </c>
       <c r="G58">
-        <v>-4.459352339704172</v>
+        <v>-4.479500319856177</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.346463524673728</v>
       </c>
       <c r="E59">
-        <v>-7.95413987390837</v>
+        <v>-9.183249232122243</v>
       </c>
       <c r="F59">
-        <v>1.064860248776381</v>
+        <v>0.3231474203394704</v>
       </c>
       <c r="G59">
-        <v>-4.281466796242514</v>
+        <v>-6.058657026452847</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.722539134954616</v>
       </c>
       <c r="E60">
-        <v>-6.973050508620595</v>
+        <v>-8.483636225729235</v>
       </c>
       <c r="F60">
-        <v>0.6037642714961861</v>
+        <v>0.4295407837386925</v>
       </c>
       <c r="G60">
-        <v>-4.50074409058168</v>
+        <v>-5.531124905315523</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.07854162900679</v>
       </c>
       <c r="E61">
-        <v>-6.637345673483976</v>
+        <v>-9.047440296632209</v>
       </c>
       <c r="F61">
-        <v>1.18291918994873</v>
+        <v>0.465018963656367</v>
       </c>
       <c r="G61">
-        <v>-5.222330459594464</v>
+        <v>-5.533587951196741</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.4062554364781</v>
       </c>
       <c r="E62">
-        <v>-6.891868555085089</v>
+        <v>-8.393075802523843</v>
       </c>
       <c r="F62">
-        <v>1.091987547401944</v>
+        <v>0.4353236858889196</v>
       </c>
       <c r="G62">
-        <v>-5.226468641518553</v>
+        <v>-5.336537659608242</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.69328047733358</v>
       </c>
       <c r="E63">
-        <v>-6.120945668493294</v>
+        <v>-9.115942522946238</v>
       </c>
       <c r="F63">
-        <v>1.017396582490661</v>
+        <v>0.003802624726598462</v>
       </c>
       <c r="G63">
-        <v>-5.182051052018151</v>
+        <v>-5.453151626229069</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.92844572815182</v>
       </c>
       <c r="E64">
-        <v>-6.291166477967615</v>
+        <v>-6.035475250072524</v>
       </c>
       <c r="F64">
-        <v>0.7722832505462668</v>
+        <v>0.2074426580104221</v>
       </c>
       <c r="G64">
-        <v>-5.479599574542307</v>
+        <v>-5.81503729076342</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.10840900616312</v>
       </c>
       <c r="E65">
-        <v>-5.497687262343615</v>
+        <v>-7.169966672370133</v>
       </c>
       <c r="F65">
-        <v>0.9715403777091117</v>
+        <v>0.283880224019107</v>
       </c>
       <c r="G65">
-        <v>-5.192575276287495</v>
+        <v>-6.636880220887492</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.22746006277195</v>
       </c>
       <c r="E66">
-        <v>-6.010106738681555</v>
+        <v>-7.115298934149536</v>
       </c>
       <c r="F66">
-        <v>0.6738385071366353</v>
+        <v>0.1398730532752404</v>
       </c>
       <c r="G66">
-        <v>-5.300326912499693</v>
+        <v>-6.167057529590743</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.27739537173088</v>
       </c>
       <c r="E67">
-        <v>-5.487040819951583</v>
+        <v>-7.071377264749141</v>
       </c>
       <c r="F67">
-        <v>0.8435310122700567</v>
+        <v>0.2863365518939536</v>
       </c>
       <c r="G67">
-        <v>-5.254297087321667</v>
+        <v>-6.483204696954524</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.26445038590784</v>
       </c>
       <c r="E68">
-        <v>-4.796131540601316</v>
+        <v>-6.243359377868639</v>
       </c>
       <c r="F68">
-        <v>0.6046907394567181</v>
+        <v>-0.09923803324963831</v>
       </c>
       <c r="G68">
-        <v>-5.995793077207627</v>
+        <v>-6.472743373050426</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.19053540807095</v>
       </c>
       <c r="E69">
-        <v>-5.68236296085042</v>
+        <v>-7.897773957934897</v>
       </c>
       <c r="F69">
-        <v>0.5501677040529266</v>
+        <v>-0.2959358916531331</v>
       </c>
       <c r="G69">
-        <v>-6.171066600238801</v>
+        <v>-6.917525097888129</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.05409515188716</v>
       </c>
       <c r="E70">
-        <v>-5.783529070181776</v>
+        <v>-7.216279376046577</v>
       </c>
       <c r="F70">
-        <v>0.6692156695694675</v>
+        <v>-0.3389857695525236</v>
       </c>
       <c r="G70">
-        <v>-6.248341354216469</v>
+        <v>-6.957062943263645</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.86385132591014</v>
       </c>
       <c r="E71">
-        <v>-5.249997848020078</v>
+        <v>-8.156829842017688</v>
       </c>
       <c r="F71">
-        <v>0.3130243721279815</v>
+        <v>0.1546450702015018</v>
       </c>
       <c r="G71">
-        <v>-5.974489716662417</v>
+        <v>-7.025256870827092</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.63201012402985</v>
       </c>
       <c r="E72">
-        <v>-6.364333032509546</v>
+        <v>-7.158917195791417</v>
       </c>
       <c r="F72">
-        <v>0.3092353557252926</v>
+        <v>-0.1822915307200715</v>
       </c>
       <c r="G72">
-        <v>-6.729807234174834</v>
+        <v>-6.888779630970637</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.36736020595333</v>
       </c>
       <c r="E73">
-        <v>-6.097442888393485</v>
+        <v>-6.975912504193443</v>
       </c>
       <c r="F73">
-        <v>0.5569293364588953</v>
+        <v>-0.3084107431490496</v>
       </c>
       <c r="G73">
-        <v>-6.105636978200645</v>
+        <v>-7.236088963495577</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.07839047008913</v>
       </c>
       <c r="E74">
-        <v>-6.027482493448986</v>
+        <v>-8.041149973491748</v>
       </c>
       <c r="F74">
-        <v>0.3737848332797313</v>
+        <v>-0.05083998047380879</v>
       </c>
       <c r="G74">
-        <v>-6.625462149322546</v>
+        <v>-7.193697427865209</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.780703123102494</v>
       </c>
       <c r="E75">
-        <v>-5.908641750065692</v>
+        <v>-7.613471831259345</v>
       </c>
       <c r="F75">
-        <v>0.4490892577059193</v>
+        <v>-0.1674617085278965</v>
       </c>
       <c r="G75">
-        <v>-6.589181880757673</v>
+        <v>-6.000646336968199</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.48323555802487</v>
       </c>
       <c r="E76">
-        <v>-6.10734666104826</v>
+        <v>-8.609423648240293</v>
       </c>
       <c r="F76">
-        <v>0.1679355302438696</v>
+        <v>-0.6404164757029023</v>
       </c>
       <c r="G76">
-        <v>-5.667747809175705</v>
+        <v>-6.677957469938769</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.184666607699464</v>
       </c>
       <c r="E77">
-        <v>-7.542537814403196</v>
+        <v>-8.057706074463791</v>
       </c>
       <c r="F77">
-        <v>0.2377349929079901</v>
+        <v>-0.2583387132206006</v>
       </c>
       <c r="G77">
-        <v>-6.441144215878083</v>
+        <v>-6.493497183036118</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.895180288803392</v>
       </c>
       <c r="E78">
-        <v>-7.401462263642241</v>
+        <v>-9.502950440115756</v>
       </c>
       <c r="F78">
-        <v>0.2719580858876788</v>
+        <v>-0.7531256582928968</v>
       </c>
       <c r="G78">
-        <v>-6.018288234146975</v>
+        <v>-6.983808840675416</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.616300579041726</v>
       </c>
       <c r="E79">
-        <v>-7.700749110809175</v>
+        <v>-9.173612639433921</v>
       </c>
       <c r="F79">
-        <v>0.007898088223924873</v>
+        <v>-0.3188798311030621</v>
       </c>
       <c r="G79">
-        <v>-6.369782096233553</v>
+        <v>-6.573959992368104</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.341242416059378</v>
       </c>
       <c r="E80">
-        <v>-8.5050468508375</v>
+        <v>-8.901089073652319</v>
       </c>
       <c r="F80">
-        <v>0.4342760644258564</v>
+        <v>-0.3240395449755638</v>
       </c>
       <c r="G80">
-        <v>-6.378856301556696</v>
+        <v>-6.651665117265877</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.067160862429176</v>
       </c>
       <c r="E81">
-        <v>-9.941623717238782</v>
+        <v>-10.78622487593537</v>
       </c>
       <c r="F81">
-        <v>0.02601726760246759</v>
+        <v>-0.7343492409594468</v>
       </c>
       <c r="G81">
-        <v>-5.930697820268938</v>
+        <v>-6.162634640750277</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.791812323858559</v>
       </c>
       <c r="E82">
-        <v>-10.43965623165435</v>
+        <v>-10.91717023034117</v>
       </c>
       <c r="F82">
-        <v>0.1388404770183738</v>
+        <v>-0.6490896411488064</v>
       </c>
       <c r="G82">
-        <v>-5.835546120379205</v>
+        <v>-6.480380801609526</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.509102177936964</v>
       </c>
       <c r="E83">
-        <v>-10.61956797550509</v>
+        <v>-11.27722014174302</v>
       </c>
       <c r="F83">
-        <v>0.3394120800910335</v>
+        <v>-0.7189603705791217</v>
       </c>
       <c r="G83">
-        <v>-5.624571674252531</v>
+        <v>-5.334130893001191</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.212552856577727</v>
       </c>
       <c r="E84">
-        <v>-11.22290562449503</v>
+        <v>-12.66806847761485</v>
       </c>
       <c r="F84">
-        <v>0.4627986079629209</v>
+        <v>-0.5133993020198699</v>
       </c>
       <c r="G84">
-        <v>-5.364670675600967</v>
+        <v>-5.896523058667041</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.907266080933003</v>
       </c>
       <c r="E85">
-        <v>-12.56547589897108</v>
+        <v>-13.15059096855415</v>
       </c>
       <c r="F85">
-        <v>0.2655203213414175</v>
+        <v>-0.6322675169150086</v>
       </c>
       <c r="G85">
-        <v>-5.710841180460399</v>
+        <v>-6.068787295803017</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.596969808508389</v>
       </c>
       <c r="E86">
-        <v>-15.08846537913053</v>
+        <v>-13.76817066829821</v>
       </c>
       <c r="F86">
-        <v>0.4121303127573089</v>
+        <v>-0.6232459361677077</v>
       </c>
       <c r="G86">
-        <v>-5.327119157549014</v>
+        <v>-5.485194396503674</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.283051903324563</v>
       </c>
       <c r="E87">
-        <v>-15.21582418212226</v>
+        <v>-16.5178283864376</v>
       </c>
       <c r="F87">
-        <v>-0.1217836706618343</v>
+        <v>-0.7748160945107555</v>
       </c>
       <c r="G87">
-        <v>-4.820989713323079</v>
+        <v>-4.810604531966385</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.978408400841967</v>
       </c>
       <c r="E88">
-        <v>-17.63109032258725</v>
+        <v>-17.79331384696403</v>
       </c>
       <c r="F88">
-        <v>0.09944658422477529</v>
+        <v>-0.5807297671618203</v>
       </c>
       <c r="G88">
-        <v>-4.363594809980754</v>
+        <v>-5.191727776629441</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.693133413948001</v>
       </c>
       <c r="E89">
-        <v>-19.02805209836943</v>
+        <v>-19.96681834558152</v>
       </c>
       <c r="F89">
-        <v>0.3092155594013496</v>
+        <v>-0.5617070835585194</v>
       </c>
       <c r="G89">
-        <v>-4.759085822284247</v>
+        <v>-5.00931009632452</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.434075374614015</v>
       </c>
       <c r="E90">
-        <v>-19.81035051166849</v>
+        <v>-20.75374033084241</v>
       </c>
       <c r="F90">
-        <v>0.237667685406584</v>
+        <v>-0.9040314520044177</v>
       </c>
       <c r="G90">
-        <v>-4.225098137345343</v>
+        <v>-5.045779065985132</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.208014900929746</v>
       </c>
       <c r="E91">
-        <v>-22.08183307391594</v>
+        <v>-21.91613620997528</v>
       </c>
       <c r="F91">
-        <v>0.3145605668659577</v>
+        <v>-0.6852424797864581</v>
       </c>
       <c r="G91">
-        <v>-5.103458700915853</v>
+        <v>-4.718730272160531</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.024044916956891</v>
       </c>
       <c r="E92">
-        <v>-23.5810930775314</v>
+        <v>-24.854318829528</v>
       </c>
       <c r="F92">
-        <v>-0.009580482111822589</v>
+        <v>-1.084418723184802</v>
       </c>
       <c r="G92">
-        <v>-3.947833327340303</v>
+        <v>-4.307308914722065</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.885290681319497</v>
       </c>
       <c r="E93">
-        <v>-26.20723666711158</v>
+        <v>-27.36928838221987</v>
       </c>
       <c r="F93">
-        <v>-0.05954561189097943</v>
+        <v>-1.129826739192282</v>
       </c>
       <c r="G93">
-        <v>-4.092378366675962</v>
+        <v>-4.635844143493798</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.787524254804793</v>
       </c>
       <c r="E94">
-        <v>-28.7144398868803</v>
+        <v>-29.83606365028511</v>
       </c>
       <c r="F94">
-        <v>-0.2101045740070191</v>
+        <v>-1.188887883896765</v>
       </c>
       <c r="G94">
-        <v>-4.088074657474909</v>
+        <v>-4.416765481886988</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.730121377877722</v>
       </c>
       <c r="E95">
-        <v>-30.76459328200286</v>
+        <v>-30.98391859937935</v>
       </c>
       <c r="F95">
-        <v>-0.2328149168344208</v>
+        <v>-0.9692540045729182</v>
       </c>
       <c r="G95">
-        <v>-3.985523888304905</v>
+        <v>-4.389387270277215</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.703531608809074</v>
       </c>
       <c r="E96">
-        <v>-32.96119979077049</v>
+        <v>-32.67608933148456</v>
       </c>
       <c r="F96">
-        <v>-0.1812811263460212</v>
+        <v>-0.9384572593412828</v>
       </c>
       <c r="G96">
-        <v>-4.321243000896858</v>
+        <v>-4.097082651887266</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.689381120796553</v>
       </c>
       <c r="E97">
-        <v>-35.45204389818649</v>
+        <v>-34.9543532835585</v>
       </c>
       <c r="F97">
-        <v>-0.4915433685338479</v>
+        <v>-1.11499216588236</v>
       </c>
       <c r="G97">
-        <v>-4.327877334157557</v>
+        <v>-4.851913519205411</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.674417816115248</v>
       </c>
       <c r="E98">
-        <v>-38.39835512858297</v>
+        <v>-37.32523585027432</v>
       </c>
       <c r="F98">
-        <v>-0.5573748560268348</v>
+        <v>-1.599337737854164</v>
       </c>
       <c r="G98">
-        <v>-3.984007658447919</v>
+        <v>-5.727678615073132</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.644781516086941</v>
       </c>
       <c r="E99">
-        <v>-40.47590805568894</v>
+        <v>-40.92340053594191</v>
       </c>
       <c r="F99">
-        <v>-0.5970633181207051</v>
+        <v>-1.489563954178436</v>
       </c>
       <c r="G99">
-        <v>-4.234817899048644</v>
+        <v>-5.557586095810918</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.594445453561878</v>
       </c>
       <c r="E100">
-        <v>-43.79275714328904</v>
+        <v>-43.17356983527226</v>
       </c>
       <c r="F100">
-        <v>-0.5872055406500523</v>
+        <v>-1.644945300806989</v>
       </c>
       <c r="G100">
-        <v>-4.640849688349176</v>
+        <v>-5.175724599492604</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.519978723219383</v>
       </c>
       <c r="E101">
-        <v>-45.28607805324344</v>
+        <v>-45.90512950703999</v>
       </c>
       <c r="F101">
-        <v>-0.7162332289927349</v>
+        <v>-1.855525925265226</v>
       </c>
       <c r="G101">
-        <v>-5.236668432325048</v>
+        <v>-5.898320684894865</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.438249071572177</v>
       </c>
       <c r="E102">
-        <v>-47.56577979581481</v>
+        <v>-48.456488744739</v>
       </c>
       <c r="F102">
-        <v>-0.9462546354159489</v>
+        <v>-1.74053937356883</v>
       </c>
       <c r="G102">
-        <v>-4.917879449620928</v>
+        <v>-5.866817533543161</v>
       </c>
     </row>
   </sheetData>
